--- a/artfynd/A 46705-2023 artfynd.xlsx
+++ b/artfynd/A 46705-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 46705-2023 artfynd.xlsx
+++ b/artfynd/A 46705-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6968552</v>
+        <v>6968550</v>
       </c>
       <c r="B2" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,48 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221725</v>
+        <v>504</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Niklasbodarna, Handog, 370 m O, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504738.9988895057</v>
+        <v>504739</v>
       </c>
       <c r="R2" t="n">
-        <v>7021024.405853219</v>
+        <v>7021024</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,24 +757,14 @@
           <t>2013-08-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2013-08-05</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>I fuktstråk i granskog, inom källområde. Kalkrikt.</t>
+          <t>En tuva med 6 skott, varav 2 st har blommat i år. I fuktstråk i granskog, inom källområde. Kalkrikt.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,15 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6968551</v>
+        <v>6968552</v>
       </c>
       <c r="B3" t="n">
-        <v>95661</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222741</v>
+        <v>221725</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504738.9988895057</v>
+        <v>504739</v>
       </c>
       <c r="R3" t="n">
-        <v>7021024.405853219</v>
+        <v>7021024</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,19 +864,9 @@
           <t>2013-08-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2013-08-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -919,15 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6968550</v>
+        <v>6968551</v>
       </c>
       <c r="B4" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98137</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,48 +914,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>504</v>
+        <v>222741</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Niklasbodarna, Handog, 370 m O, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504738.9988895057</v>
+        <v>504739</v>
       </c>
       <c r="R4" t="n">
-        <v>7021024.405853219</v>
+        <v>7021024</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,24 +971,14 @@
           <t>2013-08-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2013-08-05</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>En tuva med 6 skott, varav 2 st har blommat i år. I fuktstråk i granskog, inom källområde. Kalkrikt.</t>
+          <t>I fuktstråk i granskog, inom källområde. Kalkrikt.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 46705-2023 artfynd.xlsx
+++ b/artfynd/A 46705-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6968550</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6968552</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1007,8 +1022,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6968551</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>